--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:47</t>
+    <t xml:space="preserve">2026-09-09 23:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:47</t>
+    <t xml:space="preserve">2026-09-18 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:35</t>
+    <t xml:space="preserve">2026-09-23 13:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1500,7 +1500,9 @@
       <c r="C53" s="2" t="n">
         <v>13303</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:08</t>
+    <t xml:space="preserve">2026-10-02 15:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:51</t>
+    <t xml:space="preserve">2026-10-05 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -654,7 +654,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>139455.62</v>
+        <v>139455.63</v>
       </c>
     </row>
     <row r="4">
@@ -790,7 +790,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>133805.12</v>
+        <v>133805.13</v>
       </c>
     </row>
     <row r="12">
@@ -892,7 +892,7 @@
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>132096.12</v>
+        <v>132096.13</v>
       </c>
     </row>
     <row r="18">
